--- a/etf_holdings/2026-10-02_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:27</t>
+          <t>2026-10-02 19:06:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.22%4980</t>
+          <t>-0.6%4950</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:27</t>
+          <t>2026-10-02 19:06:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.79%1905</t>
+          <t>-1.05%1885</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:27</t>
+          <t>2026-10-02 19:06:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,17 +635,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.21%2510</t>
+          <t>-0.4%2500</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:28</t>
+          <t>2026-10-02 19:06:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.81%4975</t>
+          <t>+4.22%5185</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:28</t>
+          <t>2026-10-02 19:06:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:28</t>
+          <t>2026-10-02 19:06:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+3.4%1215</t>
+          <t>+7.41%1305</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>+7.41%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:28</t>
+          <t>2026-10-02 19:06:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:28</t>
+          <t>2026-10-02 19:06:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+2.18%3510</t>
+          <t>-1.99%3440</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:28</t>
+          <t>2026-10-02 19:06:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.51%296</t>
+          <t>-0.17%295.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>295.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:29</t>
+          <t>2026-10-02 19:06:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+5.97%1420</t>
+          <t>+2.82%1460</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+5.97%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:29</t>
+          <t>2026-10-02 19:06:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:29</t>
+          <t>2026-10-02 19:06:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:29</t>
+          <t>2026-10-02 19:06:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:29</t>
+          <t>2026-10-02 19:06:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,17 +1328,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.58%2080</t>
+          <t>+5.29%2190</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:29</t>
+          <t>2026-10-02 19:06:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/etf_holdings/2026-10-02_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:01</t>
+          <t>2026-10-02 22:50:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:01</t>
+          <t>2026-10-02 22:50:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:01</t>
+          <t>2026-10-02 22:50:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:02</t>
+          <t>2026-10-02 22:50:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:02</t>
+          <t>2026-10-02 22:50:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:02</t>
+          <t>2026-10-02 22:50:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:02</t>
+          <t>2026-10-02 22:50:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:02</t>
+          <t>2026-10-02 22:50:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:02</t>
+          <t>2026-10-02 22:50:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:04</t>
+          <t>2026-10-02 22:50:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:04</t>
+          <t>2026-10-02 22:50:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:04</t>
+          <t>2026-10-02 22:50:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:04</t>
+          <t>2026-10-02 22:50:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:04</t>
+          <t>2026-10-02 22:50:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:04</t>
+          <t>2026-10-02 22:50:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/etf_holdings/2026-10-02_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:30</t>
+          <t>2026-10-02 22:59:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:30</t>
+          <t>2026-10-02 22:59:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:30</t>
+          <t>2026-10-02 22:59:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:31</t>
+          <t>2026-10-02 22:59:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:31</t>
+          <t>2026-10-02 22:59:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:31</t>
+          <t>2026-10-02 22:59:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:31</t>
+          <t>2026-10-02 22:59:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:31</t>
+          <t>2026-10-02 22:59:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:31</t>
+          <t>2026-10-02 22:59:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:32</t>
+          <t>2026-10-02 22:59:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:32</t>
+          <t>2026-10-02 22:59:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:32</t>
+          <t>2026-10-02 22:59:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:32</t>
+          <t>2026-10-02 22:59:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:32</t>
+          <t>2026-10-02 22:59:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:32</t>
+          <t>2026-10-02 22:59:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/etf_holdings/2026-10-02_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:09</t>
+          <t>2026-10-02 23:48:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:09</t>
+          <t>2026-10-02 23:48:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:09</t>
+          <t>2026-10-02 23:48:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:10</t>
+          <t>2026-10-02 23:48:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:10</t>
+          <t>2026-10-02 23:48:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:10</t>
+          <t>2026-10-02 23:48:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:10</t>
+          <t>2026-10-02 23:48:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:10</t>
+          <t>2026-10-02 23:48:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:10</t>
+          <t>2026-10-02 23:48:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:12</t>
+          <t>2026-10-02 23:48:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:12</t>
+          <t>2026-10-02 23:48:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:12</t>
+          <t>2026-10-02 23:48:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:12</t>
+          <t>2026-10-02 23:48:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:12</t>
+          <t>2026-10-02 23:48:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:12</t>
+          <t>2026-10-02 23:48:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
